--- a/scripts/checks/results/HLR_results_15_All_lg_families_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_15_All_lg_families_Famfirst_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E2" t="n">
-        <v>1544</v>
+        <v>1877</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2788887100714704</v>
+        <v>0.2274601493467305</v>
       </c>
       <c r="H2" t="n">
-        <v>597.139684767698</v>
+        <v>552.6481254821807</v>
       </c>
       <c r="I2" t="n">
-        <v>9.159653958517076e-112</v>
+        <v>2.509992414891764e-107</v>
       </c>
       <c r="J2" t="n">
-        <v>172.1361681705525</v>
+        <v>210.6653267677102</v>
       </c>
       <c r="K2" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L2" t="n">
-        <v>66.5734049212974</v>
+        <v>62.02653060323181</v>
       </c>
       <c r="M2" t="n">
-        <v>0.111487155550876</v>
+        <v>0.1122351234777358</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7216232857673603, 'N1ratio-ArgsPreds': -0.20623521687888982}</t>
+          <t>{'const': 0.5696950682749405, 'N1ratio-ArgsPreds': -2.2180953249680244}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 5.823844912460471e-164, 'N1ratio-ArgsPreds': 9.159653958519536e-112}</t>
+          <t>{'const': 8.066049526466469e-170, 'N1ratio-ArgsPreds': 2.5099924148907162e-107}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5280991479556377}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4769278240433563}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5280991479556364)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5280991479556364)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.888871007146914)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.746014934673116)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -632,76 +632,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E3" t="n">
-        <v>1543</v>
+        <v>1876</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2789071308413007</v>
+        <v>0.2274861049803184</v>
       </c>
       <c r="H3" t="n">
-        <v>298.4037987993292</v>
+        <v>276.2176419701839</v>
       </c>
       <c r="I3" t="n">
-        <v>2.755570156435227e-110</v>
+        <v>7.179746887012252e-106</v>
       </c>
       <c r="J3" t="n">
-        <v>172.1317709564503</v>
+        <v>210.6582488777779</v>
       </c>
       <c r="K3" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L3" t="n">
-        <v>33.28890106769981</v>
+        <v>31.01680424658205</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1115565592718408</v>
+        <v>0.1122911774401801</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.7201931552183973, 'N1ratio-ArgsPreds': -0.2065815817472107, 'Fam_class': 4.7708430958967444e-05}</t>
+          <t>{'const': 0.5714134856817259, 'N1ratio-ArgsPreds': -2.212979453130236, 'Fam_class': -4.804542163441746e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 5.137391410263117e-152, 'N1ratio-ArgsPreds': 3.811566591989392e-108, 'Fam_class': 0.8426511669010686}</t>
+          <t>{'const': 1.6803457582878222e-153, 'N1ratio-ArgsPreds': 1.0515195149464727e-102, 'Fam_class': 0.8017945188393122}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5289860720930872, 'Fam_class': 0.004382625269867411}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47582782550126645, 'Fam_class': -0.005212065845856755}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5207927180821353), 'Fam_class': np.float64(0.005054203690042603)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46772702388802034), 'Fam_class': np.float64(-0.005796360279022947)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.51804058717995), 'Fam_class': np.float64(0.004291942430938809)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46511008755203403), 'Fam_class': np.float64(-0.005094667171469625)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(26.836604996574742), 'Fam_class': np.float64(0.0018420769830492932)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.632739354266075), 'Fam_class': np.float64(0.0025955633588050308)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>1.842076983027408e-05</v>
+        <v>2.595563358787079e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03941690323643662</v>
+        <v>0.06303157642181315</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8426511669015018</v>
+        <v>0.8017945188436659</v>
       </c>
     </row>
     <row r="4">
@@ -713,80 +713,80 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'Fam_class', 'latitude', 'longitude', 'Macro_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Fam_class', 'Macro_class']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E4" t="n">
-        <v>1540</v>
+        <v>1875</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3358954086663867</v>
+        <v>0.2619344462490173</v>
       </c>
       <c r="H4" t="n">
-        <v>155.7823680476198</v>
+        <v>221.8082500580563</v>
       </c>
       <c r="I4" t="n">
-        <v>4.170842569285563e-134</v>
+        <v>3.866913495936993e-123</v>
       </c>
       <c r="J4" t="n">
-        <v>158.5281234855843</v>
+        <v>201.2644667138683</v>
       </c>
       <c r="K4" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L4" t="n">
-        <v>16.03628992125313</v>
+        <v>23.80913021902456</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1029403399257041</v>
+        <v>0.1073410489140631</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5986196932832196, 'N1ratio-ArgsPreds': -0.20686377387951624, 'Fam_class': -0.00032243452209887636, 'latitude': 0.0038003308375349006, 'longitude': -4.031102623379679e-05, 'Macro_class': 0.0460251523412865}</t>
+          <t>{'const': 0.48875850821759936, 'N1ratio-ArgsPreds': -2.204672934150003, 'Fam_class': -0.0002234593954531375, 'Macro_class': 0.03939825828127002}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.3719407742721947e-99, 'N1ratio-ArgsPreds': 1.0482111701946722e-102, 'Fam_class': 0.18013535613413761, 'latitude': 1.6734942419758118e-14, 'longitude': 0.7064475226023588, 'Macro_class': 7.538214510785138e-22}</t>
+          <t>{'const': 4.8767719986787777e-104, 'N1ratio-ArgsPreds': 4.2965559556711e-106, 'Fam_class': 0.2348447770269036, 'Macro_class': 2.3055494328075716e-20}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5297086713992855, 'Fam_class': -0.029619705700309657, 'latitude': 0.16943928622756507, 'longitude': -0.008689873893935239, 'Macro_class': 0.20984359433892663}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47404178412692904, 'Fam_class': -0.024241333374890633, 'Macro_class': 0.18654570057031447}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5096588369431844), 'Fam_class': np.float64(-0.034150565916667), 'latitude': np.float64(0.1937156151161411), 'longitude': np.float64(-0.00959879471274713), 'Macro_class': np.float64(0.2412012499406551)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4746933756270998), 'Fam_class': np.float64(-0.02743351278883546), 'Macro_class': np.float64(0.21116941052515278)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4827354770349647), 'Fam_class': np.float64(-0.027846431236075636), 'latitude': np.float64(0.16091195426469565), 'longitude': np.float64(-0.007822668978830055), 'Macro_class': np.float64(0.20254120521156874)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4633437786944902), 'Fam_class': np.float64(-0.02357720805344872), 'Macro_class': np.float64(0.18560264348520186)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.303354078817495), 'Fam_class': np.float64(0.07754237325854889), 'latitude': np.float64(2.5892657025283503), 'longitude': np.float64(0.006119414995235006), 'Macro_class': np.float64(4.10229398085548)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.468745725488876), 'Fam_class': np.float64(0.055588473959560715), 'Macro_class': np.float64(3.4448341268694946)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.05698827782508598</v>
+        <v>0.03444834126869889</v>
       </c>
       <c r="V4" t="n">
-        <v>44.05026406779006</v>
+        <v>87.51341876144889</v>
       </c>
       <c r="W4" t="n">
-        <v>2.611690873579224e-27</v>
+        <v>2.305549432809763e-20</v>
       </c>
     </row>
     <row r="5">
@@ -798,80 +798,80 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'Fam_class', 'latitude', 'longitude', 'Macro_class', 'Nlen_freq', 'Vlen_freq']</t>
+          <t>['N1ratio-ArgsPreds', 'Fam_class', 'Macro_class', 'Nlen_freq', 'Vlen_freq']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E5" t="n">
-        <v>1538</v>
+        <v>1873</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3450160878646344</v>
+        <v>0.2696056640049715</v>
       </c>
       <c r="H5" t="n">
-        <v>115.7356110594801</v>
+        <v>138.2736376216228</v>
       </c>
       <c r="I5" t="n">
-        <v>1.676257582139809e-136</v>
+        <v>5.057909186436992e-125</v>
       </c>
       <c r="J5" t="n">
-        <v>156.3509300478628</v>
+        <v>199.1725880957002</v>
       </c>
       <c r="K5" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L5" t="n">
-        <v>11.76552043485529</v>
+        <v>14.70385385504836</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1016586021117444</v>
+        <v>0.1063388083799787</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.6613995821693979, 'N1ratio-ArgsPreds': -0.20022658501321283, 'Fam_class': -0.0005341528657764051, 'latitude': 0.0039047828681669614, 'longitude': -0.00013919989562287803, 'Macro_class': 0.0412498936283439, 'Nlen_freq': -0.0524527716501398, 'Vlen_freq': 0.0452162032076389}</t>
+          <t>{'const': 0.5046776201284596, 'N1ratio-ArgsPreds': -2.155636240753618, 'Fam_class': -0.00037507656564068144, 'Macro_class': 0.033532467808258686, 'Nlen_freq': -0.42228642356768914, 'Vlen_freq': 0.5326304691843444}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 3.467951301744247e-38, 'N1ratio-ArgsPreds': 2.6913691577771065e-95, 'Fam_class': 0.029582124451353393, 'latitude': 2.5250829575456674e-15, 'longitude': 0.20243259343687858, 'Macro_class': 3.54186449501802e-16, 'Nlen_freq': 1.0990348773320784e-05, 'Vlen_freq': 1.0268744561068696e-05}</t>
+          <t>{'const': 4.7074025917597657e-57, 'N1ratio-ArgsPreds': 2.6206041863872668e-101, 'Fam_class': 0.05095891044144157, 'Macro_class': 1.5464474263993172e-13, 'Nlen_freq': 0.00010126742949760375, 'Vlen_freq': 1.079569303844813e-05}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5127130591165694, 'Fam_class': -0.04906872434218563, 'latitude': 0.17409632222572471, 'longitude': -0.030007411173214038, 'Macro_class': 0.18807164136869683, 'Nlen_freq': -0.16839277217585022, 'Vlen_freq': 0.17778809172835097}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46349806978942354, 'Fam_class': -0.04068907485571176, 'Macro_class': 0.1587719349034505, 'Nlen_freq': -0.1405620037501508, 'Vlen_freq': 0.1688113034162252}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.49343054122089797), 'Fam_class': np.float64(-0.055442836886884554), 'latitude': np.float64(0.1997530673854666), 'longitude': np.float64(-0.03249893906373088), 'Macro_class': np.float64(0.20570605550188176), 'Nlen_freq': np.float64(-0.11177807024820487), 'Vlen_freq': np.float64(0.1121500562205195)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4651843715052284), 'Fam_class': np.float64(-0.045082628434283095), 'Macro_class': np.float64(0.16938491657459173), 'Nlen_freq': np.float64(-0.0896577084057821), 'Vlen_freq': np.float64(0.10143271487191431)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4591232942452651), 'Fam_class': np.float64(-0.04493960793348434), 'latitude': np.float64(0.16498741947445694), 'longitude': np.float64(-0.026315641903408214), 'Macro_class': np.float64(0.17011830467541128), 'Nlen_freq': np.float64(-0.09103368573942058), 'Vlen_freq': np.float64(0.09134048898379135)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44911300406873617), 'Fam_class': np.float64(-0.03856823063612457), 'Macro_class': np.float64(0.14688409858336846), 'Nlen_freq': np.float64(-0.07693410846742123), 'Vlen_freq': np.float64(0.08713697129816651)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.07941993186243), 'Fam_class': np.float64(0.20195683612152884), 'latitude': np.float64(2.7220848584840414), 'longitude': np.float64(0.06925130087884143), 'Macro_class': np.float64(2.894023758563606), 'Nlen_freq': np.float64(0.8287131939303586), 'Vlen_freq': np.float64(0.834308492779811)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.170249042364464), 'Fam_class': np.float64(0.1487508414401298), 'Macro_class': np.float64(2.1574938416648703), 'Nlen_freq': np.float64(0.5918857045676935), 'Vlen_freq': np.float64(0.7592851767017494)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.009120679198247772</v>
+        <v>0.007671217755954252</v>
       </c>
       <c r="V5" t="n">
-        <v>10.70835813445597</v>
+        <v>9.835913388709598</v>
       </c>
       <c r="W5" t="n">
-        <v>2.407140461332174e-05</v>
+        <v>5.631105420963074e-05</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_15_All_lg_families_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_15_All_lg_families_Famfirst_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2274601493467305</v>
+        <v>0.2216711997682284</v>
       </c>
       <c r="H2" t="n">
-        <v>552.6481254821807</v>
+        <v>534.5772144639448</v>
       </c>
       <c r="I2" t="n">
-        <v>2.509992414891764e-107</v>
+        <v>2.805806715175607e-104</v>
       </c>
       <c r="J2" t="n">
-        <v>210.6653267677102</v>
+        <v>210.7278626313512</v>
       </c>
       <c r="K2" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L2" t="n">
-        <v>62.02653060323181</v>
+        <v>60.01615014140037</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1122351234777358</v>
+        <v>0.1122684404002936</v>
       </c>
       <c r="N2" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5696950682749405, 'N1ratio-ArgsPreds': -2.2180953249680244}</t>
+          <t>{'const': 0.5567146824557327, 'N1ratio-ArgsPreds': -2.146484111162861}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 8.066049526466469e-170, 'N1ratio-ArgsPreds': 2.5099924148907162e-107}</t>
+          <t>{'const': 2.2155466928380838e-166, 'N1ratio-ArgsPreds': 2.8058067151748e-104}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4769278240433563}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4708197104712461}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47081971047124643)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4708197104712464)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.746014934673116)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.16711997682283)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2274861049803184</v>
+        <v>0.221736132632494</v>
       </c>
       <c r="H3" t="n">
-        <v>276.2176419701839</v>
+        <v>267.2467541282687</v>
       </c>
       <c r="I3" t="n">
-        <v>7.179746887012252e-106</v>
+        <v>7.53359073578489e-103</v>
       </c>
       <c r="J3" t="n">
-        <v>210.6582488777779</v>
+        <v>210.7102824471191</v>
       </c>
       <c r="K3" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L3" t="n">
-        <v>31.01680424658205</v>
+        <v>30.01686516281625</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1122911774401801</v>
+        <v>0.1123189138843918</v>
       </c>
       <c r="N3" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5714134856817259, 'N1ratio-ArgsPreds': -2.212979453130236, 'Fam_class': -4.804542163441746e-05}</t>
+          <t>{'const': 0.5594672996035288, 'N1ratio-ArgsPreds': -2.1387202477778535, 'Fam_class': -7.564945240760837e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.6803457582878222e-153, 'N1ratio-ArgsPreds': 1.0515195149464727e-102, 'Fam_class': 0.8017945188393122}</t>
+          <t>{'const': 5.379681521513522e-150, 'N1ratio-ArgsPreds': 1.0320607663038064e-99, 'Fam_class': 0.6924256437313685}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47582782550126645, 'Fam_class': -0.005212065845856755}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4691167489202811, 'Fam_class': -0.00823607566206608}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46772702388802034), 'Fam_class': np.float64(-0.005796360279022947)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4615418300813215), 'Fam_class': np.float64(-0.009133783850248652)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46511008755203403), 'Fam_class': np.float64(-0.005094667171469625)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4589790803977487), 'Fam_class': np.float64(-0.008058093091154971)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.632739354266075), 'Fam_class': np.float64(0.0025955633588050308)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.06617962427631), 'Fam_class': np.float64(0.006493286426571948)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>2.595563358787079e-05</v>
+        <v>6.493286426567657e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06303157642181315</v>
+        <v>0.1565202477849163</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8017945188436659</v>
+        <v>0.6924256437348864</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2619344462490173</v>
+        <v>0.2568493439592348</v>
       </c>
       <c r="H4" t="n">
-        <v>221.8082500580563</v>
+        <v>216.013857580065</v>
       </c>
       <c r="I4" t="n">
-        <v>3.866913495936993e-123</v>
+        <v>2.391569004212337e-120</v>
       </c>
       <c r="J4" t="n">
-        <v>201.2644667138683</v>
+        <v>201.2035907111796</v>
       </c>
       <c r="K4" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L4" t="n">
-        <v>23.80913021902456</v>
+        <v>23.18014068719064</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1073410489140631</v>
+        <v>0.1073085817126291</v>
       </c>
       <c r="N4" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.48875850821759936, 'N1ratio-ArgsPreds': -2.204672934150003, 'Fam_class': -0.0002234593954531375, 'Macro_class': 0.03939825828127002}</t>
+          <t>{'const': 0.4759888597113267, 'N1ratio-ArgsPreds': -2.1283025723595106, 'Fam_class': -0.00025296341176453646, 'Macro_class': 0.03963539429346937}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 4.8767719986787777e-104, 'N1ratio-ArgsPreds': 4.2965559556711e-106, 'Fam_class': 0.2348447770269036, 'Macro_class': 2.3055494328075716e-20}</t>
+          <t>{'const': 2.661723004130498e-100, 'N1ratio-ArgsPreds': 7.408631313803836e-103, 'Fam_class': 0.17825901796088212, 'Macro_class': 1.3695135232499387e-20}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47404178412692904, 'Fam_class': -0.024241333374890633, 'Macro_class': 0.18654570057031447}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46683168801592134, 'Fam_class': -0.027540527164709, 'Macro_class': 0.1883423818238196}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4746933756270998), 'Fam_class': np.float64(-0.02743351278883546), 'Macro_class': np.float64(0.21116941052515278)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46814807108830736), 'Fam_class': np.float64(-0.031084286040385028), 'Macro_class': np.float64(0.2124084751565065)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4633437786944902), 'Fam_class': np.float64(-0.02357720805344872), 'Macro_class': np.float64(0.18560264348520186)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4567108953294115), 'Fam_class': np.float64(-0.02680953279693525), 'Macro_class': np.float64(0.18738519505749102)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.468745725488876), 'Fam_class': np.float64(0.055588473959560715), 'Macro_class': np.float64(3.4448341268694946)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.858484191259265), 'Fam_class': np.float64(0.07187510487899469), 'Macro_class': np.float64(3.511321132673396)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03444834126869889</v>
+        <v>0.03511321132674072</v>
       </c>
       <c r="V4" t="n">
-        <v>87.51341876144889</v>
+        <v>88.59209192977873</v>
       </c>
       <c r="W4" t="n">
-        <v>2.305549432809763e-20</v>
+        <v>1.369513523251479e-20</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2696056640049715</v>
+        <v>0.2657158657219123</v>
       </c>
       <c r="H5" t="n">
-        <v>138.2736376216228</v>
+        <v>135.556739758906</v>
       </c>
       <c r="I5" t="n">
-        <v>5.057909186436992e-125</v>
+        <v>7.158313357665104e-123</v>
       </c>
       <c r="J5" t="n">
-        <v>199.1725880957002</v>
+        <v>198.8030330298154</v>
       </c>
       <c r="K5" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L5" t="n">
-        <v>14.70385385504836</v>
+        <v>14.38819594858723</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1063388083799787</v>
+        <v>0.1061415018845784</v>
       </c>
       <c r="N5" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.5046776201284596, 'N1ratio-ArgsPreds': -2.155636240753618, 'Fam_class': -0.00037507656564068144, 'Macro_class': 0.033532467808258686, 'Nlen_freq': -0.42228642356768914, 'Vlen_freq': 0.5326304691843444}</t>
+          <t>{'const': 0.49666219231992514, 'N1ratio-ArgsPreds': -2.0794987072970708, 'Fam_class': -0.0004085471162185734, 'Macro_class': 0.03351768772919311, 'Nlen_freq': -0.4583225475710338, 'Vlen_freq': 0.5661226375859597}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 4.7074025917597657e-57, 'N1ratio-ArgsPreds': 2.6206041863872668e-101, 'Fam_class': 0.05095891044144157, 'Macro_class': 1.5464474263993172e-13, 'Nlen_freq': 0.00010126742949760375, 'Vlen_freq': 1.079569303844813e-05}</t>
+          <t>{'const': 1.2789872833262011e-55, 'N1ratio-ArgsPreds': 3.199367485890473e-98, 'Fam_class': 0.033169445271977155, 'Macro_class': 1.460951534164385e-13, 'Nlen_freq': 2.2739211578144714e-05, 'Vlen_freq': 2.6234273289648736e-06}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.46349806978942354, 'Fam_class': -0.04068907485571176, 'Macro_class': 0.1587719349034505, 'Nlen_freq': -0.1405620037501508, 'Vlen_freq': 0.1688113034162252}</t>
+          <t>{'N1ratio-ArgsPreds': -0.45612682348928507, 'Fam_class': -0.044479171409794106, 'Macro_class': 0.1592718138086843, 'Nlen_freq': -0.15327235179880694, 'Vlen_freq': 0.18032405719078692}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4651843715052284), 'Fam_class': np.float64(-0.045082628434283095), 'Macro_class': np.float64(0.16938491657459173), 'Nlen_freq': np.float64(-0.0896577084057821), 'Vlen_freq': np.float64(0.10143271487191431)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.45873592425780246), 'Fam_class': np.float64(-0.049193872126034946), 'Macro_class': np.float64(0.16955595967348097), 'Nlen_freq': np.float64(-0.09766072855481152), 'Vlen_freq': np.float64(0.10825566001887667)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.44911300406873617), 'Fam_class': np.float64(-0.03856823063612457), 'Macro_class': np.float64(0.14688409858336846), 'Nlen_freq': np.float64(-0.07693410846742123), 'Vlen_freq': np.float64(0.08713697129816651)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4423865178459994), 'Fam_class': np.float64(-0.04220551669299832), 'Macro_class': np.float64(0.14742781941566868), 'Nlen_freq': np.float64(-0.0840878095118275), 'Vlen_freq': np.float64(0.09331308004320403)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.170249042364464), 'Fam_class': np.float64(0.1487508414401298), 'Macro_class': np.float64(2.1574938416648703), 'Nlen_freq': np.float64(0.5918857045676935), 'Vlen_freq': np.float64(0.7592851767017494)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.570583117190875), 'Fam_class': np.float64(0.17813056393229595), 'Macro_class': np.float64(2.1734961937659016), 'Nlen_freq': np.float64(0.7070759708497387), 'Vlen_freq': np.float64(0.8707330907149402)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.007671217755954252</v>
+        <v>0.008866521762677548</v>
       </c>
       <c r="V5" t="n">
-        <v>9.835913388709598</v>
+        <v>11.30828958862242</v>
       </c>
       <c r="W5" t="n">
-        <v>5.631105420963074e-05</v>
+        <v>1.313066589934197e-05</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_15_All_lg_families_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_15_All_lg_families_Famfirst_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2216711997682284</v>
+        <v>0.2215000730459347</v>
       </c>
       <c r="H2" t="n">
-        <v>534.5772144639448</v>
+        <v>534.0471112616439</v>
       </c>
       <c r="I2" t="n">
-        <v>2.805806715175607e-104</v>
+        <v>3.450072936797282e-104</v>
       </c>
       <c r="J2" t="n">
-        <v>210.7278626313512</v>
+        <v>210.7741941668376</v>
       </c>
       <c r="K2" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L2" t="n">
-        <v>60.01615014140037</v>
+        <v>59.96981860591393</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1122684404002936</v>
+        <v>0.112293124223142</v>
       </c>
       <c r="N2" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5567146824557327, 'N1ratio-ArgsPreds': -2.146484111162861}</t>
+          <t>{'const': 0.5562505171853904, 'N1ratio-ArgsPreds': -2.142785220917257}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 2.2155466928380838e-166, 'N1ratio-ArgsPreds': 2.8058067151748e-104}</t>
+          <t>{'const': 2.611073940529163e-166, 'N1ratio-ArgsPreds': 3.45007293679726e-104}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4708197104712461}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47063794263311826}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47081971047124643)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47063794263311876)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4708197104712464)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47063794263311887)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.16711997682283)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.150007304593487)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.221736132632494</v>
+        <v>0.2215641810573831</v>
       </c>
       <c r="H3" t="n">
-        <v>267.2467541282687</v>
+        <v>266.9805227027272</v>
       </c>
       <c r="I3" t="n">
-        <v>7.53359073578489e-103</v>
+        <v>9.268235090907063e-103</v>
       </c>
       <c r="J3" t="n">
-        <v>210.7102824471191</v>
+        <v>210.7568373065672</v>
       </c>
       <c r="K3" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L3" t="n">
-        <v>30.01686516281625</v>
+        <v>29.99358773309218</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1123189138843918</v>
+        <v>0.1123437299075518</v>
       </c>
       <c r="N3" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5594672996035288, 'N1ratio-ArgsPreds': -2.1387202477778535, 'Fam_class': -7.564945240760837e-05}</t>
+          <t>{'const': 0.5589856011599725, 'N1ratio-ArgsPreds': -2.1350738576957373, 'Fam_class': -7.517046515621833e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 5.379681521513522e-150, 'N1ratio-ArgsPreds': 1.0320607663038064e-99, 'Fam_class': 0.6924256437313685}</t>
+          <t>{'const': 6.677300873815543e-150, 'N1ratio-ArgsPreds': 1.2702135053794654e-99, 'Fam_class': 0.6943182797021796}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4691167489202811, 'Fam_class': -0.00823607566206608}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46894423106275424, 'Fam_class': -0.008183927561609813}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4615418300813215), 'Fam_class': np.float64(-0.009133783850248652)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4613534260903031), 'Fam_class': np.float64(-0.009074586919709438)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4589790803977487), 'Fam_class': np.float64(-0.008058093091154971)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4587917225361234), 'Fam_class': np.float64(-0.008006747869677248)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.06617962427631), 'Fam_class': np.float64(0.006493286426571948)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.04898446676632), 'Fam_class': np.float64(0.006410801144858116)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>6.493286426567657e-05</v>
+        <v>6.410801144840494e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1565202477849163</v>
+        <v>0.1544978102890628</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6924256437348864</v>
+        <v>0.6943182797062395</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2568493439592348</v>
+        <v>0.2567052339018107</v>
       </c>
       <c r="H4" t="n">
-        <v>216.013857580065</v>
+        <v>215.8508017362219</v>
       </c>
       <c r="I4" t="n">
-        <v>2.391569004212337e-120</v>
+        <v>2.867528165102606e-120</v>
       </c>
       <c r="J4" t="n">
-        <v>201.2035907111796</v>
+        <v>201.2426076464075</v>
       </c>
       <c r="K4" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L4" t="n">
-        <v>23.18014068719064</v>
+        <v>23.16713504211467</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1073085817126291</v>
+        <v>0.1073293907447507</v>
       </c>
       <c r="N4" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.4759888597113267, 'N1ratio-ArgsPreds': -2.1283025723595106, 'Fam_class': -0.00025296341176453646, 'Macro_class': 0.03963539429346937}</t>
+          <t>{'const': 0.47549729366172055, 'N1ratio-ArgsPreds': -2.1248032393549123, 'Fam_class': -0.0002525010139435483, 'Macro_class': 0.03965103062451359}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 2.661723004130498e-100, 'N1ratio-ArgsPreds': 7.408631313803836e-103, 'Fam_class': 0.17825901796088212, 'Macro_class': 1.3695135232499387e-20}</t>
+          <t>{'const': 3.37836526600286e-100, 'N1ratio-ArgsPreds': 8.888602376169492e-103, 'Fam_class': 0.17911157189957666, 'Macro_class': 1.3348856395963182e-20}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.46683168801592134, 'Fam_class': -0.027540527164709, 'Macro_class': 0.1883423818238196}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46668840876273543, 'Fam_class': -0.027490185181807212, 'Macro_class': 0.18841668369174217}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46814807108830736), 'Fam_class': np.float64(-0.031084286040385028), 'Macro_class': np.float64(0.2124084751565065)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.467986322751285), 'Fam_class': np.float64(-0.031023368613961395), 'Macro_class': np.float64(0.2124691981309034)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4567108953294115), 'Fam_class': np.float64(-0.02680953279693525), 'Macro_class': np.float64(0.18738519505749102)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.456553098615244), 'Fam_class': np.float64(-0.02675953634864669), 'Macro_class': np.float64(0.18745946987130344)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.858484191259265), 'Fam_class': np.float64(0.07187510487899469), 'Macro_class': np.float64(3.511321132673396)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.844073185518074), 'Fam_class': np.float64(0.07160727855945433), 'Macro_class': np.float64(3.514105284443012)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03511321132674072</v>
+        <v>0.03514105284442759</v>
       </c>
       <c r="V4" t="n">
-        <v>88.59209192977873</v>
+        <v>88.64514737427562</v>
       </c>
       <c r="W4" t="n">
-        <v>1.369513523251479e-20</v>
+        <v>1.334885639597344e-20</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2657158657219123</v>
+        <v>0.2655869534128203</v>
       </c>
       <c r="H5" t="n">
-        <v>135.556739758906</v>
+        <v>135.4671913996731</v>
       </c>
       <c r="I5" t="n">
-        <v>7.158313357665104e-123</v>
+        <v>8.431280695249332e-123</v>
       </c>
       <c r="J5" t="n">
-        <v>198.8030330298154</v>
+        <v>198.8379352656748</v>
       </c>
       <c r="K5" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L5" t="n">
-        <v>14.38819594858723</v>
+        <v>14.38121550141536</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1061415018845784</v>
+        <v>0.1061601362870661</v>
       </c>
       <c r="N5" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.49666219231992514, 'N1ratio-ArgsPreds': -2.0794987072970708, 'Fam_class': -0.0004085471162185734, 'Macro_class': 0.03351768772919311, 'Nlen_freq': -0.4583225475710338, 'Vlen_freq': 0.5661226375859597}</t>
+          <t>{'const': 0.49652766931315534, 'N1ratio-ArgsPreds': -2.076017194287955, 'Fam_class': -0.0004076623078644501, 'Macro_class': 0.03354091503258436, 'Nlen_freq': -0.4654514735555309, 'Vlen_freq': 0.5663991687897232}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 1.2789872833262011e-55, 'N1ratio-ArgsPreds': 3.199367485890473e-98, 'Fam_class': 0.033169445271977155, 'Macro_class': 1.460951534164385e-13, 'Nlen_freq': 2.2739211578144714e-05, 'Vlen_freq': 2.6234273289648736e-06}</t>
+          <t>{'const': 1.2627084477625751e-55, 'N1ratio-ArgsPreds': 3.959981272341936e-98, 'Fam_class': 0.03357606360786202, 'Macro_class': 1.4135893769768456e-13, 'Nlen_freq': 2.159276758215745e-05, 'Vlen_freq': 2.607955080594042e-06}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.45612682348928507, 'Fam_class': -0.044479171409794106, 'Macro_class': 0.1592718138086843, 'Nlen_freq': -0.15327235179880694, 'Vlen_freq': 0.18032405719078692}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4559731193089045, 'Fam_class': -0.04438284092333239, 'Macro_class': 0.1593821870173286, 'Nlen_freq': -0.15375492171117486, 'Vlen_freq': 0.18044583122953328}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.45873592425780246), 'Fam_class': np.float64(-0.049193872126034946), 'Macro_class': np.float64(0.16955595967348097), 'Nlen_freq': np.float64(-0.09766072855481152), 'Vlen_freq': np.float64(0.10825566001887667)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4585402540022576), 'Fam_class': np.float64(-0.049080845291872344), 'Macro_class': np.float64(0.16965499314907867), 'Nlen_freq': np.float64(-0.09792704689958502), 'Vlen_freq': np.float64(0.10828333547654159)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4423865178459994), 'Fam_class': np.float64(-0.04220551669299832), 'Macro_class': np.float64(0.14742781941566868), 'Nlen_freq': np.float64(-0.0840878095118275), 'Vlen_freq': np.float64(0.09331308004320403)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4421863799312043), 'Fam_class': np.float64(-0.04211200787694005), 'Macro_class': np.float64(0.1475294280983914), 'Nlen_freq': np.float64(-0.08432673336870719), 'Vlen_freq': np.float64(0.09334541130732464)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.570583117190875), 'Fam_class': np.float64(0.17813056393229595), 'Macro_class': np.float64(2.1734961937659016), 'Nlen_freq': np.float64(0.7070759708497387), 'Vlen_freq': np.float64(0.8707330907149402)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.552879459666336), 'Fam_class': np.float64(0.17734212074274608), 'Macro_class': np.float64(2.176493215503844), 'Nlen_freq': np.float64(0.7110997960637035), 'Vlen_freq': np.float64(0.8713365812133611)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.008866521762677548</v>
+        <v>0.008881719511009689</v>
       </c>
       <c r="V5" t="n">
-        <v>11.30828958862242</v>
+        <v>11.32568431445097</v>
       </c>
       <c r="W5" t="n">
-        <v>1.313066589934197e-05</v>
+        <v>1.290691702370897e-05</v>
       </c>
     </row>
   </sheetData>
